--- a/datasets/day2_advanced_excel_and_power_bi/01_advanced_formulas/d2_m1_advanced_formulas_start.xlsx
+++ b/datasets/day2_advanced_excel_and_power_bi/01_advanced_formulas/d2_m1_advanced_formulas_start.xlsx
@@ -191,33 +191,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Products" displayName="Products" ref="A1:D19" headerRowCount="1">
-  <autoFilter ref="A1:D19"/>
-  <tableColumns count="4">
-    <tableColumn id="1" name="SKU"/>
-    <tableColumn id="2" name="Product"/>
-    <tableColumn id="3" name="Category"/>
-    <tableColumn id="4" name="List Price"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium4" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Customers" displayName="Customers" ref="A1:E13" headerRowCount="1">
-  <autoFilter ref="A1:E13"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Customer ID"/>
-    <tableColumn id="2" name="Customer Name"/>
-    <tableColumn id="3" name="Country"/>
-    <tableColumn id="4" name="City"/>
-    <tableColumn id="5" name="Score"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium5" showRowStripes="1"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1328,7 +1301,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>86.98999999999999</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3">
@@ -1348,7 +1321,7 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>1462.12</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="4">
@@ -1368,7 +1341,7 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>167.73</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
@@ -1388,7 +1361,7 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>730.12</v>
+        <v>800</v>
       </c>
     </row>
     <row r="6">
@@ -1408,7 +1381,7 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>572.75</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7">
@@ -1428,7 +1401,7 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>239.47</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8">
@@ -1448,7 +1421,7 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1505.26</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="9">
@@ -1468,7 +1441,7 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>107.3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10">
@@ -1488,7 +1461,7 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1337.73</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="11">
@@ -1508,7 +1481,7 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>745.25</v>
+        <v>600</v>
       </c>
     </row>
     <row r="12">
@@ -1528,7 +1501,7 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1019</v>
+        <v>900</v>
       </c>
     </row>
     <row r="13">
@@ -1548,7 +1521,7 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>157.97</v>
+        <v>200</v>
       </c>
     </row>
     <row r="14">
@@ -1568,7 +1541,7 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>863.4</v>
+        <v>600</v>
       </c>
     </row>
     <row r="15">
@@ -1588,7 +1561,7 @@
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1339.7</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="16">
@@ -1608,7 +1581,7 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>113.64</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17">
@@ -1628,7 +1601,7 @@
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18">
@@ -1648,7 +1621,7 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>721.84</v>
+        <v>700</v>
       </c>
     </row>
     <row r="19">
@@ -1668,14 +1641,11 @@
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>862.75</v>
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -2012,9 +1982,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 

--- a/datasets/day2_advanced_excel_and_power_bi/01_advanced_formulas/d2_m1_advanced_formulas_start.xlsx
+++ b/datasets/day2_advanced_excel_and_power_bi/01_advanced_formulas/d2_m1_advanced_formulas_start.xlsx
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5" customWidth="1" min="1" max="1"/>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" s="4" t="n"/>
       <c r="J4" s="4" t="n"/>
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" s="4" t="n"/>
       <c r="J5" s="4" t="n"/>
@@ -691,7 +691,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>OnePlus 13</t>
+          <t>iPad Air 6</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
@@ -709,16 +709,16 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45938</v>
+        <v>45694</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>C012</t>
+          <t>C008</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Galaxy S24</t>
+          <t>Ring Doorbell Pro</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
@@ -736,20 +736,20 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45458</v>
+        <v>45922</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>C010</t>
+          <t>C002</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Echo Dot 6</t>
+          <t>Galaxy S24</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I8" s="4" t="n"/>
       <c r="J8" s="4" t="n"/>
@@ -790,20 +790,20 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45856</v>
+        <v>46084</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>C005</t>
+          <t>C007</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Surface Go 4</t>
+          <t>USB-C Hub 7in1</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10" s="4" t="n"/>
       <c r="J10" s="4" t="n"/>
@@ -817,20 +817,20 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45383</v>
+        <v>45796</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>C007</t>
+          <t>C003</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HP Spectre x360</t>
+          <t>Surface Go 4</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I11" s="4" t="n"/>
       <c r="J11" s="4" t="n"/>
@@ -844,20 +844,20 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46317</v>
+        <v>46200</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>C004</t>
+          <t>C009</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ThinkPad X1</t>
+          <t>Pixel 9 Pro</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" s="4" t="n"/>
       <c r="J12" s="4" t="n"/>
@@ -871,16 +871,16 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45857</v>
+        <v>45944</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>C001</t>
+          <t>C011</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Surface Go 4</t>
+          <t>Echo Dot 6</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
@@ -898,20 +898,20 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45994</v>
+        <v>46365</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>C005</t>
+          <t>C006</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Galaxy S24</t>
+          <t>HP Spectre x360</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" s="4" t="n"/>
       <c r="J14" s="4" t="n"/>
@@ -925,16 +925,16 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45453</v>
+        <v>45682</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>C007</t>
+          <t>C012</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Echo Dot 6</t>
+          <t>Galaxy Tab S10</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
@@ -952,16 +952,16 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46287</v>
+        <v>46210</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>C010</t>
+          <t>C001</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Galaxy S24</t>
+          <t>Wireless Mouse Pro</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
@@ -979,16 +979,16 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46107</v>
+        <v>45734</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>C010</t>
+          <t>C004</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ThinkPad X1</t>
+          <t>OnePlus 13</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
@@ -1006,16 +1006,16 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46011</v>
+        <v>46347</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>C006</t>
+          <t>C010</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Bluetooth Headphones</t>
+          <t>Google Nest Hub 3</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
@@ -1033,20 +1033,20 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45508</v>
+        <v>45902</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>C005</t>
+          <t>C002</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ThinkPad X1</t>
+          <t>Laptop Sleeve 15in</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I19" s="4" t="n"/>
       <c r="J19" s="4" t="n"/>
@@ -1060,20 +1060,20 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45671</v>
+        <v>46065</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>C004</t>
+          <t>C007</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ThinkPad X1</t>
+          <t>iPad Air 6</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I20" s="4" t="n"/>
       <c r="J20" s="4" t="n"/>
@@ -1087,16 +1087,16 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45306</v>
+        <v>45824</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>C002</t>
+          <t>C003</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>OnePlus 13</t>
+          <t>Ring Doorbell Pro</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
@@ -1106,141 +1106,6 @@
       <c r="J21" s="4" t="n"/>
       <c r="L21" s="5" t="n"/>
       <c r="M21" s="4" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>O0021</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>45939</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>C004</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Galaxy Tab S10</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="I22" s="4" t="n"/>
-      <c r="J22" s="4" t="n"/>
-      <c r="L22" s="5" t="n"/>
-      <c r="M22" s="4" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>O0022</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>45884</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>C010</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>iPad Air 6</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" s="4" t="n"/>
-      <c r="J23" s="4" t="n"/>
-      <c r="L23" s="5" t="n"/>
-      <c r="M23" s="4" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>O0023</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>45522</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>C010</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Google Nest Hub 3</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I24" s="4" t="n"/>
-      <c r="J24" s="4" t="n"/>
-      <c r="L24" s="5" t="n"/>
-      <c r="M24" s="4" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>O0024</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>46343</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>C003</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Google Nest Hub 3</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I25" s="4" t="n"/>
-      <c r="J25" s="4" t="n"/>
-      <c r="L25" s="5" t="n"/>
-      <c r="M25" s="4" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>O0025</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>46363</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>C010</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>ThinkPad X1</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" s="4" t="n"/>
-      <c r="J26" s="4" t="n"/>
-      <c r="L26" s="5" t="n"/>
-      <c r="M26" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2173,7 +2038,7 @@
         </is>
       </c>
       <c r="F45" s="10">
-        <f>_xlfn._xlws.SORT(_xlfn._xlws.FILTER(Orders!A2:E26,Orders!E2:E26&gt;=2,"none"),1,1)</f>
+        <f>_xlfn._xlws.SORT(_xlfn._xlws.FILTER(Orders!A2:E21,Orders!E2:E21&gt;=2,"none"),1,1)</f>
         <v/>
       </c>
     </row>

--- a/datasets/day2_advanced_excel_and_power_bi/01_advanced_formulas/d2_m1_advanced_formulas_start.xlsx
+++ b/datasets/day2_advanced_excel_and_power_bi/01_advanced_formulas/d2_m1_advanced_formulas_start.xlsx
@@ -2079,7 +2079,7 @@
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t>Three sheets of data: Orders (25 rows), Products, Customers - plus a Tiers table.</t>
+          <t>Three sheets of data: Orders (20 rows), Products, Customers - plus a Tiers table.</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Copy it down to F26.</t>
+          <t xml:space="preserve">   Copy it down to F21.</t>
         </is>
       </c>
     </row>
